--- a/outputs/spotlight/spotlight-database.xlsx
+++ b/outputs/spotlight/spotlight-database.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -908,6 +908,429 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Terms of Submission — guest/story portal</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tamron Hall Show</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Talent bookers</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>New York (national)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>tamronhallshow.com submission portal (Summerdale Productions)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/booking/tv/</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Real, published submission route -- not a general contact guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gospel artist interview/special programming</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Word Network</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Talent bookers / Segment producers</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Television / Music (Gospel)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass -- 'about' page only</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/booking/tv/</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Confirmed as covering this exact talent category (Kirk Franklin, CeCe Winans, etc. cited as past guests); submission route not yet found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Faith/inspirational programming block</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bounce TV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Segment producers</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Television / Music (Gospel)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/booking/tv/</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Secondary candidate; not independently fetched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R&amp;B Money podcast (Tank &amp; J. Valentine)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>iHeartRadio</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Talent bookers</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Music / Podcast</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>iheart.com podcast page -- direct submission route not yet found</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/booking/radio-podcasts/</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Strong thematic fit (faith, family, legacy) for legacy R&amp;B/gospel artists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Totally Booked with Zibby (Zibby Owens)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Independent podcast</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Talent bookers</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Books / Podcast</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/booking/radio-podcasts/</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Book-side target once a publication window exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Online for Authors</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Independent podcast</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Talent bookers</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Books / Podcast</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/booking/radio-podcasts/</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Book-side target; covers inspirational memoirs specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Taste of Soul (event, Oct 17 2026)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Los Angeles Sentinel / Bakewell Media</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Event organizers and programmers</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Music / Live Event</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vendor route confirmed (tasteofsoulla.net); performer/talent route NOT publicly found -- direct-relationship booking</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/spotlight/live-events/</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>300,000+ attendee free festival; largest one-day West Coast festival of its kind, per source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Devine Jamz Gospel Network</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Independent gospel radio promoter</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Publicists and agency representatives</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Music (Gospel)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>devinejamz.com -- consultation-first submission process</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/spotlight/music-radio/</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Candidate for gospel radio promotion, not vetted/recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gospel Airplay Now</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Independent gospel radio servicing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Publicists and agency representatives</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Music (Gospel)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>gospelairplaynow.com/servicing-options -- not independently fetched</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>booking-desk research, migrated from outputs/spotlight/music-radio/</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Candidate for gospel radio servicing, not vetted/recommended.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/spotlight/spotlight-database.xlsx
+++ b/outputs/spotlight/spotlight-database.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1331,6 +1331,382 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Editorial pitch inbox</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AARP The Magazine</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Journalists and editors</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>News / Lifestyle</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>pubspitches@aarp.org -- one-page story-idea letter per their own writer's guidelines</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>aarp.org writer's guidelines page</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Real, verified, publicly posted pitch email -- highest-confidence contact route found this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Editor (general)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Essence</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Journalists and editors</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>News / Culture</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mailing address: 135 West 50th Street, New York, NY 10020 -- no email route confirmed</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>muckrack.com/audreywilliamswrites.com summaries</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Address only; needs a follow-up pass for a real email/portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Festival talent programming</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>New Orleans Jazz &amp; Heritage Festival</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Event organizers and programmers</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>National (New Orleans)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Online application, nojazzfest.com -- 2027 window June 15-Sept 1, 2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>nojazzfest.com/apply</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TIME-CRITICAL: window closes approximately Sept 1, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Festival talent programming</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Toronto Jazz Festival</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Event organizers and programmers</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>International (Canada)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Year-round submissions; Dec 15 deadline for following year</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>torontojazz.com/artist-submissions</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Real, open, standing route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Festival talent programming</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Beaches International Jazz Festival</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Event organizers and programmers</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>International (Canada)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Online submission, Oct 1 2026-Feb 1 2027 window for 2027</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>beachesjazz.com/artists</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Window not yet open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Festival talent programming</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hyde Park Jazz Festival</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Event organizers and programmers</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Email submission, Dec 15-March 15 window</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>hydeparkjazzfestival.org/music-submissions</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Window not yet open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Festival talent programming</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SLO Jazz Festival</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Event organizers and programmers</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>San Francisco (Central Coast CA)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Online submission, Sept 30-Dec 15 window</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>slojazzfest.org/artist-submission</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Window not yet open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cruise entertainment booking agency</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Warshaw Entertainment / G.L. Berg / Premier Entertainment / Landau Music</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Publicists and agency representatives</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vocal reel (&lt;=2 min) + movement reel (&lt;=2 min) submitted to agency</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>agency websites (warshawentertainment.com, glberg.com, premierentertainmentint.com, landaumusic.com)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Royal Caribbean specifically named as seeking R&amp;B/Soul/Gospel/Jazz singers. Positioning care needed given Freda's stature.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/spotlight/spotlight-database.xlsx
+++ b/outputs/spotlight/spotlight-database.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -484,6 +484,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence Level</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>How Verified</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,6 +541,16 @@
           <t>Confirmed as a real, current desk route. Entertainment-specific desk contact not separately verified this pass.</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,6 +598,16 @@
           <t>UNVERIFIED — CURRENCY RISK. Source's own date not visible in this pass. Staff-specific contact info like this ages fast; re-verify directly before using in a real pitch.</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -625,6 +655,16 @@
           <t>Same currency-risk flag as above — name and role not independently re-confirmed this pass.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -672,6 +712,16 @@
           <t>Same currency-risk flag.</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -719,6 +769,16 @@
           <t>Same currency-risk flag.</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -766,6 +826,16 @@
           <t>Confirmed real partner relationship (since 1999, per HR reporting), not a submission route.</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -813,6 +883,16 @@
           <t>Confirmed — official Recording Academy source, Jan 28-31 2026 window.</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -860,6 +940,16 @@
           <t>Confirmed dates (Mar 11-15, 2026); submission/access route not researched this pass.</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -907,6 +997,16 @@
           <t>Confirmed dates (Mar 13-14, 2026, Luxe Sunset Blvd Hotel); access route not researched this pass.</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -954,6 +1054,16 @@
           <t>Real, published submission route -- not a general contact guess.</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1001,6 +1111,16 @@
           <t>Confirmed as covering this exact talent category (Kirk Franklin, CeCe Winans, etc. cited as past guests); submission route not yet found.</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1048,6 +1168,16 @@
           <t>Secondary candidate; not independently fetched.</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1095,6 +1225,16 @@
           <t>Strong thematic fit (faith, family, legacy) for legacy R&amp;B/gospel artists.</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1142,6 +1282,16 @@
           <t>Book-side target once a publication window exists.</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1189,6 +1339,16 @@
           <t>Book-side target; covers inspirational memoirs specifically.</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1236,6 +1396,16 @@
           <t>300,000+ attendee free festival; largest one-day West Coast festival of its kind, per source.</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1283,6 +1453,16 @@
           <t>Candidate for gospel radio promotion, not vetted/recommended.</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1330,6 +1510,16 @@
           <t>Candidate for gospel radio servicing, not vetted/recommended.</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1377,6 +1567,16 @@
           <t>Real, verified, publicly posted pitch email -- highest-confidence contact route found this pass.</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1424,6 +1624,16 @@
           <t>Address only; needs a follow-up pass for a real email/portal.</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1471,6 +1681,16 @@
           <t>TIME-CRITICAL: window closes approximately Sept 1, 2026.</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1518,6 +1738,16 @@
           <t>Real, open, standing route.</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1565,6 +1795,16 @@
           <t>Window not yet open.</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1612,6 +1852,16 @@
           <t>Window not yet open.</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1659,6 +1909,16 @@
           <t>Window not yet open.</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1704,6 +1964,863 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>Royal Caribbean specifically named as seeking R&amp;B/Soul/Gospel/Jazz singers. Positioning care needed given Freda's stature.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Predates Aug 16 2026 confidence-level upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Andy Lassner, Corey Palent, Graehme Morphy, Walter Williams III (EPs, w/ Jennifer Hudson)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The Jennifer Hudson Show</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Talent bookers / Segment producers</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>No public submission portal found -- relationship-based route</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>BroadwayWorld, TheWrap, Deadline, THR (Season 5 renewal coverage)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Confirmed current</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Cross-referenced across 4 independent trade sources, all reporting the same Season 5 renewal</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No segment/booking producer names found this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Simone Swink (EP)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Good Morning America</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Segment producers</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Aggregated search summary</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Single source only, not cross-referenced</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Anastasia Elyse Williams</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Good Morning America</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Talent bookers</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>No usable email (ZoomInfo shows redacted a***@abc.com only -- not recorded as real)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LinkedIn (self-identified), ZoomInfo</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>LinkedIn self-ID cross-referenced against ZoomInfo aggregator listing</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Entertainment Booker and Coordinating Entertainment Producer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Melissa Rose Farley</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Good Morning America (3rd hour)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Talent bookers</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Single LinkedIn source only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>"Third hour" branding needs reconfirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Katie Distler</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NBC News / Today</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Talent bookers</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Single LinkedIn source only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Senior Booking Producer, NBC News.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Brian Teta, Candi Carter (co-EPs)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The View</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Segment producers</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ABC News press site (detpress.com), official bio page, season-premiere press release</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Confirmed current</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Cross-referenced ABC's own press site bio page against a dated 2026 season press release</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Teta leads segment producing/studio floor; Carter guides from control room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Alex Duda (EP/showrunner)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The Kelly Clarkson Show</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Segment producers</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>IMDb news article</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Single named-source article, not cross-referenced</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>SHOW ENDING after Season 7, fall 2026 -- confirmed across 5 independent sources. Do not prioritize.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jon Tower (interim EP)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CBS Mornings</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Segment producers</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>TVInsider, Variety, Deadline</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Confirmed current (as interim)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Cross-referenced across 3 independent trade sources reporting the same March 2026 leadership change</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Status explicitly interim -- re-verify before relying on long-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kaci Sokoloff (VP of Bookings, CBS News)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CBS News (network-wide)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Talent bookers</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>TVInsider/Variety/Deadline (CBS Mornings leadership coverage)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Found within cross-referenced leadership coverage but her specific new title not independently re-confirmed in a second source</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>HIGH VALUE if confirmed -- centralized bookings authority across CBS News broadcast + streaming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tammy Fine</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NBC News (moving to Talent Development)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A -- leaving booking-adjacent work</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Variety, Deadline</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Confirmed current</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Cross-referenced across 2 independent trade sources, both dated August 2026</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NOT a current booking target -- moving out of newsmaker-booking role. Recorded to prevent a future misdirected pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Nate Smith (Artistic Director)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Newport Jazz Festival</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Event organizers and programmers</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass -- official site found, direct submission route not yet extracted</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>newportjazz.org/artistic-director (official/primary) plus 7 independent trade/music sources</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Confirmed current</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Cross-referenced against the festival's own official site directly -- strongest verification in this pass</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Succeeded Christian McBride (10-year AD) for the 2026 festival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Maurin Auxemery (Director of Programming)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Montreal International Jazz Festival</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Event organizers and programmers</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>International (Canada)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Billboard Canada</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Single source only, not cross-referenced</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nanette Wong (VP Global Brand Marketing)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fenty Beauty</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brand and partnership contacts</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Glossy (2023, dated), LinkedIn</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Two sources found but the clearest one (Glossy) is dated 2023 -- three years stale relative to today</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>RE-VERIFY before use given source age.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kelly Thompson (SVP PR &amp; Communications, L'Oreal Luxe USA)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>L'Oreal Luxe (Armani, Lancome, Kiehl's, YSL, and others)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brand and partnership contacts</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Harvard Kennedy School bio page (undated)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Single source, undated, not cross-referenced</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Covers PR/communications, not necessarily talent-casting decisions specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Clarisse Glasgow (Influencer Marketing Manager)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fenty Skin</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brand and partnership contacts</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Not confirmed this pass</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Likely current</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Single LinkedIn source only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Influencer-marketing role specifically -- may not be the right decision-maker for a legacy-artist ambassador conversation.</t>
         </is>
       </c>
     </row>
